--- a/output/pdf_financials_xlsx/SPA.xlsx
+++ b/output/pdf_financials_xlsx/SPA.xlsx
@@ -7100,13 +7100,13 @@
         <v>0</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.301992</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.592621</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.277422</v>
       </c>
     </row>
     <row r="93">
@@ -11944,7 +11944,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -13772,7 +13776,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SPA.xlsx
+++ b/output/pdf_financials_xlsx/SPA.xlsx
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.030776</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.043326</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.021505</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.090998</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.151666</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.102777</v>
       </c>
     </row>
     <row r="13">
@@ -2325,25 +2325,25 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.837153</v>
+        <v>-1.867929</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.432458</v>
+        <v>-0.475784</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.794316</v>
+        <v>-0.815821</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.965432</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.876462</v>
+        <v>-0.96746</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.140536</v>
+        <v>-2.292202</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.465246</v>
+        <v>-2.568023</v>
       </c>
     </row>
     <row r="28">
@@ -2471,25 +2471,25 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.828937</v>
+        <v>-1.859713</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.427735</v>
+        <v>-0.471061</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.709769</v>
+        <v>-0.731274</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-0.965432</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.804304</v>
+        <v>-0.895302</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.064185</v>
+        <v>-2.215851</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.390043</v>
+        <v>-2.49282</v>
       </c>
     </row>
     <row r="30">
@@ -9430,13 +9430,13 @@
         </is>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.058128</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.062154</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.073089</v>
       </c>
     </row>
     <row r="125">
@@ -9505,13 +9505,13 @@
         </is>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.058128</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.062154</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.073089</v>
       </c>
     </row>
     <row r="126">
@@ -20500,7 +20500,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -28790,7 +28794,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -28888,7 +28892,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -30042,7 +30046,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -30140,7 +30144,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -32328,7 +32332,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">

--- a/output/pdf_financials_xlsx/SPA.xlsx
+++ b/output/pdf_financials_xlsx/SPA.xlsx
@@ -1480,25 +1480,25 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-1.837153</v>
+        <v>-2.866476</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.432458</v>
+        <v>-0.095722</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-0.794316</v>
+        <v>-0.641718</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-0.965432</v>
+        <v>-0.78477</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-0.876462</v>
+        <v>-0.7086440000000001</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-2.140536</v>
+        <v>-4.485959</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-2.465246</v>
+        <v>-4.930492</v>
       </c>
     </row>
     <row r="17">
@@ -1553,25 +1553,25 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>1.029323</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.336736</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.152598</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.180662</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.167818</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>2.345423</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>-0</v>
+        <v>2.465246</v>
       </c>
     </row>
     <row r="18">
@@ -2325,25 +2325,25 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.867929</v>
+        <v>-2.897252</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.475784</v>
+        <v>-0.139048</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.815821</v>
+        <v>-0.663223</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.965432</v>
+        <v>-0.78477</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.96746</v>
+        <v>-0.799642</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.292202</v>
+        <v>-4.637625</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.568023</v>
+        <v>-5.033269</v>
       </c>
     </row>
     <row r="28">
@@ -2471,25 +2471,25 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.859713</v>
+        <v>-2.889036</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.471061</v>
+        <v>-0.134325</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.731274</v>
+        <v>-0.578676</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.965432</v>
+        <v>-0.78477</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.895302</v>
+        <v>-0.727484</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.215851</v>
+        <v>-4.561274</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.49282</v>
+        <v>-4.958066</v>
       </c>
     </row>
     <row r="30">
@@ -2631,25 +2631,25 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-35.90900464542525</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-351.7853784918827</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-23.77960412517648</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0</v>
+        <v>-23.02101252596302</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0</v>
+        <v>-23.68156648472294</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0</v>
+        <v>-52.28364771055642</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="32">
@@ -5030,13 +5030,13 @@
         <v>0</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.9533430000000001</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.377719</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.633768</v>
       </c>
     </row>
     <row r="65">
@@ -5249,13 +5249,13 @@
         <v>0</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.19848</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.09867099999999999</v>
       </c>
     </row>
     <row r="68">
@@ -7708,10 +7708,10 @@
         <v>0.158758</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>-0.097581</v>
+        <v>-0.01086</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>-0.073266</v>
       </c>
     </row>
     <row r="102">
@@ -8083,10 +8083,10 @@
         <v>1.082462</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.071044</v>
+        <v>0.015677</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.750329</v>
+        <v>0.677063</v>
       </c>
     </row>
     <row r="107">
@@ -18984,7 +18984,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -19078,7 +19082,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -25084,7 +25092,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -29086,7 +29098,11 @@
           <t>Net loss before income tax recovery</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -29180,7 +29196,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -30530,7 +30550,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -31468,7 +31492,11 @@
           <t>Deferred Income Tax Recovery 11</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -32426,7 +32454,11 @@
           <t>Deferred Income Tax Recovery 10</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -33102,7 +33134,11 @@
           <t>Deferred Income Tax Recovery (Expense) 9</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
